--- a/ig/document/CodeSystem-MedCom-message-codes-CS-TEMP.xlsx
+++ b/ig/document/CodeSystem-MedCom-message-codes-CS-TEMP.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -127,7 +127,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>Code</t>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>Pregnancy Measurement Report</t>
+  </si>
+  <si>
+    <t>CON</t>
+  </si>
+  <si>
+    <t>Consultation Note</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -638,6 +644,18 @@
       </c>
       <c r="D7" s="2"/>
     </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="C8" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="D8" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ig/document/CodeSystem-MedCom-message-codes-CS-TEMP.xlsx
+++ b/ig/document/CodeSystem-MedCom-message-codes-CS-TEMP.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
